--- a/temp/BBVA_VISA_20250130.xlsx
+++ b/temp/BBVA_VISA_20250130.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-1166285.11</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-1166285,11</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>10200</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10200,0</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>91500</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>91500,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>15600</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15600,0</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>34050</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>34050,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>9120.99</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9120,99</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>19200</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>19200,0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>7199</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7199,0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -671,12 +687,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>650.37</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>650,37</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>2454</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2454,0</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>6600</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6600,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>5200</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5200,0</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>29201.5</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>29201,5</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -796,12 +822,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>6400</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6400,0</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -821,12 +849,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>12974.96</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>12974,96</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -846,12 +876,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>11862.41</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>11862,41</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -871,12 +903,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>90800</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>90800,0</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -896,12 +930,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>25089</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>25089,0</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -921,12 +957,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>49581</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>49581,0</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -946,12 +984,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1500</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1500,0</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -971,12 +1011,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>17949</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>17949,0</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -996,12 +1038,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>3299</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3299,0</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1065,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>4000</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4000,0</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1092,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>27200</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>27200,0</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1119,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>2400</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2400,0</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1146,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>9211.41</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9211,41</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1173,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>47500</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>47500,0</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1200,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>16000</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>16000,0</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1227,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>181586</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>181586,0</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1254,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>81345.64</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>81345,64</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1281,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>28787.38</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>28787,38</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1308,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>16200</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>16200,0</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1335,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>12400</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>12400,0</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1362,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>10203.04</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>10203,04</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1389,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>5670</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5670,0</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1416,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>12615.98</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>12615,98</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1443,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>14080</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>14080,0</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1470,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>13100</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>13100,0</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1497,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>209.96</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>209,96</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1524,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>2204.58</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2204,58</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1551,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>3149.4</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3149,4</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>

--- a/temp/BBVA_VISA_20250130.xlsx
+++ b/temp/BBVA_VISA_20250130.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>071512K MERPAGO*THOMAS</t>
+          <t>MERPAGO*THOMAS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000988* ELECTROPAGO*REC PIZZA SA</t>
+          <t>ELECTROPAGO*REC PIZZA SA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>891733K MERPAGO*LUCKY13</t>
+          <t>MERPAGO*LUCKY13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>504070* TOMATE</t>
+          <t>TOMATE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000175K AXION BONPLAND</t>
+          <t>AXION BONPLAND</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002157* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>093709Q NETFLIX.COM 42785628363430465</t>
+          <t>NETFLIX.COM 42785628363430465</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>000001* AUTOPISTAS URBAN 000000003616132</t>
+          <t>AUTOPISTAS URBAN 000000003616132</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>152724K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>062195K MERPAGO*THOMAS</t>
+          <t>MERPAGO*THOMAS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>537338K MERPAGO*QR</t>
+          <t>MERPAGO*QR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>157805K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>412396K MERPAGO*VEAEXPRESS</t>
+          <t>MERPAGO*VEAEXPRESS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>000877K AXION BONPLAND</t>
+          <t>AXION BONPLAND</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>994537* BBVA SEGUROS A2052000420510-023-000</t>
+          <t>BBVA SEGUROS A2052000420510-023-000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>990897* Melé</t>
+          <t>Melé</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>022849K PEDIDOSYA RESTAURANTE</t>
+          <t>PEDIDOSYA RESTAURANTE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>011651* TRIUNFO COOP D0000007681097-094-004</t>
+          <t>TRIUNFO COOP D0000007681097-094-004</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>112297K PEDIDOSYA PROPINAS</t>
+          <t>PEDIDOSYA PROPINAS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>006603* RAPPI</t>
+          <t>RAPPI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>362503V Spotify</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>990015K MERPAGO*QR</t>
+          <t>MERPAGO*QR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>987147K MERPAGO*KOPI</t>
+          <t>MERPAGO*KOPI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>521578K MERPAGO*QR</t>
+          <t>MERPAGO*QR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>873678K MERPAGO*METROGASSA</t>
+          <t>MERPAGO*METROGASSA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>279419K MERPAGO*THOMAS</t>
+          <t>MERPAGO*THOMAS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>218966K MERPAGO*THOMAS</t>
+          <t>MERPAGO*THOMAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>292402K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>135742* PATENTES</t>
+          <t>PATENTES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>003474* EDENORDIGITAL</t>
+          <t>EDENORDIGITAL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002130K RINCON NORTENO COLEGIALES</t>
+          <t>RINCON NORTENO COLEGIALES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>158049K MERPAGO*LUCKY13</t>
+          <t>MERPAGO*LUCKY13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>002547K AXION BONPLAND</t>
+          <t>AXION BONPLAND</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>943671K MERPAGO*TELEPASE</t>
+          <t>MERPAGO*TELEPASE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>120415* EXPERTA SEGURO0000032131884-015-004</t>
+          <t>EXPERTA SEGURO0000032131884-015-004</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>003593* DLO*RAPPI</t>
+          <t>DLO*RAPPI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>003289* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
